--- a/data/words.xlsx
+++ b/data/words.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="몸으로말해요_100" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="몸으로말해요_110" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이구동성_60" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="영어로설명하기_80" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자료출처" sheetId="5" state="visible" r:id="rId5"/>
@@ -683,7 +683,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>중2 교실 레크리에이션  |  게임 제시어 240개</t>
+          <t>중2 교실 레크리에이션  |  게임 제시어 250개</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -707,7 +707,7 @@
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>몸으로 말해요 100 · 이구동성 60 · 영어로 설명하기 80  |  2026-10-29 정리</t>
+          <t>몸으로 말해요 110 · 이구동성 60 · 영어로 설명하기 80  |  2026-10-29 정리</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -767,11 +767,11 @@
       </c>
       <c r="B8" s="63" t="inlineStr">
         <is>
-          <t>속담 / 운동·스포츠·동물·직업</t>
+          <t>속담 / 운동·스포츠·동물</t>
         </is>
       </c>
       <c r="C8" s="63" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D8" s="63" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B12" s="69" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1030,7 +1030,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>몸으로 말해요  |  제시어 100</t>
+          <t>몸으로 말해요  |  제시어 110</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1052,7 +1052,7 @@
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>속담 50 · 단어 50(운동·스포츠 20 / 동물 20 / 직업 10)  ·  학생이 맞히기 쉬운 것 위주  ·  웹앱에서는 속담과 단어를 따로 출제</t>
+          <t>속담 50 · 단어 60(운동·스포츠 30 / 동물 30)  ·  학생이 맞히기 쉬운 것 위주  ·  웹앱에서는 속담과 단어를 따로 출제</t>
         </is>
       </c>
       <c r="B3" s="1" t="n"/>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>토끼</t>
+          <t>피구</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F76" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G76" s="37" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>고양이</t>
+          <t>발야구</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G77" s="37" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>강아지</t>
+          <t>스케이트</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F78" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G78" s="37" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>펭귄</t>
+          <t>등산</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G79" s="37" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>캥거루</t>
+          <t>낚시</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G80" s="37" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>고릴라</t>
+          <t>자전거 타기</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G81" s="37" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>코끼리</t>
+          <t>팔굽혀펴기</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G82" s="37" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>기린</t>
+          <t>윗몸일으키기</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G83" s="37" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
-          <t>원숭이</t>
+          <t>요가</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F84" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G84" s="37" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>동물</t>
+          <t>운동·스포츠</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>개구리</t>
+          <t>서핑</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>동물명 정확히</t>
+          <t>종목·동작명 정확히</t>
         </is>
       </c>
       <c r="G85" s="37" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C86" s="32" t="inlineStr">
         <is>
-          <t>악어</t>
+          <t>토끼</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C87" s="32" t="inlineStr">
         <is>
-          <t>뱀</t>
+          <t>고양이</t>
         </is>
       </c>
       <c r="D87" s="18" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C88" s="32" t="inlineStr">
         <is>
-          <t>닭</t>
+          <t>강아지</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C89" s="32" t="inlineStr">
         <is>
-          <t>돼지</t>
+          <t>펭귄</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C90" s="32" t="inlineStr">
         <is>
-          <t>오리</t>
+          <t>캥거루</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="C91" s="32" t="inlineStr">
         <is>
-          <t>사자</t>
+          <t>고릴라</t>
         </is>
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="C92" s="32" t="inlineStr">
         <is>
-          <t>거북이</t>
+          <t>코끼리</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="E92" s="18" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="C93" s="32" t="inlineStr">
         <is>
-          <t>나비</t>
+          <t>기린</t>
         </is>
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="C94" s="32" t="inlineStr">
         <is>
-          <t>낙타</t>
+          <t>원숭이</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="E94" s="18" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C95" s="32" t="inlineStr">
         <is>
-          <t>문어</t>
+          <t>개구리</t>
         </is>
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>쉬움</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="B96" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
         <is>
-          <t>소방관</t>
+          <t>악어</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G96" s="36" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="B97" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
         <is>
-          <t>경찰관</t>
+          <t>뱀</t>
         </is>
       </c>
       <c r="D97" s="18" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G97" s="36" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="B98" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
-          <t>요리사</t>
+          <t>닭</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G98" s="36" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B99" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
         <is>
-          <t>의사</t>
+          <t>돼지</t>
         </is>
       </c>
       <c r="D99" s="18" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G99" s="36" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="B100" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>선생님</t>
+          <t>오리</t>
         </is>
       </c>
       <c r="D100" s="18" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G100" s="36" t="inlineStr">
@@ -4430,17 +4430,17 @@
       </c>
       <c r="B101" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
         <is>
-          <t>가수</t>
+          <t>사자</t>
         </is>
       </c>
       <c r="D101" s="18" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G101" s="36" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="B102" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
         <is>
-          <t>미용사</t>
+          <t>거북이</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G102" s="36" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B103" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
         <is>
-          <t>간호사</t>
+          <t>나비</t>
         </is>
       </c>
       <c r="D103" s="18" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G103" s="36" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="B104" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>마술사</t>
+          <t>낙타</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G104" s="36" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="B105" s="18" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>동물</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
         <is>
-          <t>버스 기사</t>
+          <t>문어</t>
         </is>
       </c>
       <c r="D105" s="18" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>직업명 정확히</t>
+          <t>동물명 정확히</t>
         </is>
       </c>
       <c r="G105" s="36" t="inlineStr">
@@ -4599,16 +4599,356 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="24" customHeight="1"/>
-    <row r="107" ht="24" customHeight="1"/>
-    <row r="108" ht="24" customHeight="1"/>
-    <row r="109" ht="24" customHeight="1"/>
-    <row r="110" ht="24" customHeight="1"/>
-    <row r="111" ht="24" customHeight="1"/>
-    <row r="112" ht="24" customHeight="1"/>
-    <row r="113" ht="24" customHeight="1"/>
-    <row r="114" ht="24" customHeight="1"/>
-    <row r="115" ht="24" customHeight="1"/>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="18" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>호랑이</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G106" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="18" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>곰</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G107" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>말</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G108" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>소</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G109" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="18" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>쥐</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G110" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="18" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>상어</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G111" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>판다</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G112" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>코알라</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G113" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="18" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>하마</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G114" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="C115" s="32" t="inlineStr">
+        <is>
+          <t>독수리</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>미사용</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>동물명 정확히</t>
+        </is>
+      </c>
+      <c r="G115" s="36" t="inlineStr">
+        <is>
+          <t>https://www.yugacrew.com/crewletter/charades-word-cards-printable</t>
+        </is>
+      </c>
+    </row>
     <row r="116" ht="24" customHeight="1"/>
     <row r="117" ht="24" customHeight="1"/>
     <row r="118" ht="24" customHeight="1"/>
@@ -4705,7 +5045,7 @@
     <mergeCell ref="A1:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E6:E105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"미사용,사용,보류"</formula1>
     </dataValidation>
   </dataValidations>
